--- a/seed-files/Production Tracker 2026.xlsx
+++ b/seed-files/Production Tracker 2026.xlsx
@@ -567,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -616,10 +616,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A2" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
@@ -641,21 +639,15 @@
           <t>COMP-4471</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
-        <is>
-          <t>Stock confirmed via Teams (Warner/Dominguez) - 5.1 L, date extended lot.</t>
-        </is>
-      </c>
+      <c r="F2" s="8" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A3" s="6" t="n">
+        <v>2</v>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>5697812</t>
+          <t>5697610</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -665,17 +657,17 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>WO-88355</t>
+          <t>WO-88292</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>COMP-4512</t>
+          <t>COMP-4472</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>Filling component, safety stock item - order created for CSAB follow-up.</t>
+          <t>Awaiting batch release</t>
         </is>
       </c>
     </row>

--- a/seed-files/Production Tracker 2026.xlsx
+++ b/seed-files/Production Tracker 2026.xlsx
@@ -567,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -616,8 +616,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="n">
-        <v>1</v>
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
@@ -639,7 +641,11 @@
           <t>COMP-4471</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr"/>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>Stock confirmed via Teams (Warner/Dominguez) - 5.1 L, date extended lot.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n">

--- a/seed-files/Production Tracker 2026.xlsx
+++ b/seed-files/Production Tracker 2026.xlsx
@@ -567,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -616,10 +616,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A2" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
@@ -641,11 +639,7 @@
           <t>COMP-4471</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
-        <is>
-          <t>Stock confirmed via Teams (Warner/Dominguez) - 5.1 L, date extended lot.</t>
-        </is>
-      </c>
+      <c r="F2" s="8" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n">
